--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/5.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/5.xlsx
@@ -426,13 +426,13 @@
         <v>-2.853386052115128</v>
       </c>
       <c r="E2">
-        <v>-14.06418416604878</v>
+        <v>-17.80959167089241</v>
       </c>
       <c r="F2">
-        <v>-2.996510710744952</v>
+        <v>-4.052090180090932</v>
       </c>
       <c r="G2">
-        <v>-9.238288889883702</v>
+        <v>-8.275174767243646</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.453368043516115</v>
       </c>
       <c r="E3">
-        <v>-13.79214051784986</v>
+        <v>-18.35200522312634</v>
       </c>
       <c r="F3">
-        <v>-2.566728851150485</v>
+        <v>-3.848242216140418</v>
       </c>
       <c r="G3">
-        <v>-9.329462617866856</v>
+        <v>-8.48825851928113</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.102796288098945</v>
       </c>
       <c r="E4">
-        <v>-15.21427898648633</v>
+        <v>-18.53468837646025</v>
       </c>
       <c r="F4">
-        <v>-2.911883868507552</v>
+        <v>-4.083741270184498</v>
       </c>
       <c r="G4">
-        <v>-9.75162393436676</v>
+        <v>-8.639771776254094</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.706314852342345</v>
       </c>
       <c r="E5">
-        <v>-14.6916554862152</v>
+        <v>-18.47470354529575</v>
       </c>
       <c r="F5">
-        <v>-1.897808091144037</v>
+        <v>-4.046221197042097</v>
       </c>
       <c r="G5">
-        <v>-9.816624947824003</v>
+        <v>-8.703915160113157</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.25679972271094</v>
       </c>
       <c r="E6">
-        <v>-16.27536633502147</v>
+        <v>-19.20434386405295</v>
       </c>
       <c r="F6">
-        <v>-2.029516851454352</v>
+        <v>-3.634025577409064</v>
       </c>
       <c r="G6">
-        <v>-8.658955527509594</v>
+        <v>-8.76876605575641</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.721452532248918</v>
       </c>
       <c r="E7">
-        <v>-14.84137460126395</v>
+        <v>-19.39040357819395</v>
       </c>
       <c r="F7">
-        <v>-2.359441505743548</v>
+        <v>-4.103917815014485</v>
       </c>
       <c r="G7">
-        <v>-9.738799956935212</v>
+        <v>-9.196674926473651</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.090018662672424</v>
       </c>
       <c r="E8">
-        <v>-17.8340125534824</v>
+        <v>-20.14027834252571</v>
       </c>
       <c r="F8">
-        <v>-2.33132588772513</v>
+        <v>-4.055727541356624</v>
       </c>
       <c r="G8">
-        <v>-9.031504864544573</v>
+        <v>-8.955653596566664</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.354248609490456</v>
       </c>
       <c r="E9">
-        <v>-15.67063384685849</v>
+        <v>-20.08448825479929</v>
       </c>
       <c r="F9">
-        <v>-2.340219240161586</v>
+        <v>-3.717111656277257</v>
       </c>
       <c r="G9">
-        <v>-8.97269131576827</v>
+        <v>-8.748220801196645</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.51394088009474</v>
       </c>
       <c r="E10">
-        <v>-16.70699712837693</v>
+        <v>-20.13919435436993</v>
       </c>
       <c r="F10">
-        <v>-2.365001507751138</v>
+        <v>-3.583119087037423</v>
       </c>
       <c r="G10">
-        <v>-9.921298836087804</v>
+        <v>-8.947622946204399</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.571370922103076</v>
       </c>
       <c r="E11">
-        <v>-16.61759925460999</v>
+        <v>-20.53828058378403</v>
       </c>
       <c r="F11">
-        <v>-1.480517183616383</v>
+        <v>-3.578484371418759</v>
       </c>
       <c r="G11">
-        <v>-9.136108262704415</v>
+        <v>-8.588794377368016</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.539316712612703</v>
       </c>
       <c r="E12">
-        <v>-16.73009728976562</v>
+        <v>-21.69817282973685</v>
       </c>
       <c r="F12">
-        <v>-1.005782310174195</v>
+        <v>-3.128673416392003</v>
       </c>
       <c r="G12">
-        <v>-8.666849113780826</v>
+        <v>-8.297067166012427</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.428241428376965</v>
       </c>
       <c r="E13">
-        <v>-16.43817221895475</v>
+        <v>-21.97696129312729</v>
       </c>
       <c r="F13">
-        <v>-1.698630462610507</v>
+        <v>-3.248461969776034</v>
       </c>
       <c r="G13">
-        <v>-8.410343457703945</v>
+        <v>-8.295782679673598</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.253834829750017</v>
       </c>
       <c r="E14">
-        <v>-18.71830184913092</v>
+        <v>-21.48118830407118</v>
       </c>
       <c r="F14">
-        <v>-0.7120705652657824</v>
+        <v>-3.156151191510265</v>
       </c>
       <c r="G14">
-        <v>-8.300214418617013</v>
+        <v>-8.019813922669968</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.031400071509279</v>
       </c>
       <c r="E15">
-        <v>-18.23716477678351</v>
+        <v>-23.31106829452269</v>
       </c>
       <c r="F15">
-        <v>-0.6991107572489841</v>
+        <v>-3.122675208028331</v>
       </c>
       <c r="G15">
-        <v>-7.108549187609423</v>
+        <v>-7.170387283994533</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.769408030277445</v>
       </c>
       <c r="E16">
-        <v>-19.45109030207234</v>
+        <v>-23.73259432472484</v>
       </c>
       <c r="F16">
-        <v>-0.539655002414496</v>
+        <v>-2.230931071975441</v>
       </c>
       <c r="G16">
-        <v>-6.819905265615938</v>
+        <v>-7.734736277787944</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.478554159445068</v>
       </c>
       <c r="E17">
-        <v>-20.68022904044402</v>
+        <v>-24.75679700348418</v>
       </c>
       <c r="F17">
-        <v>-0.3209817470560798</v>
+        <v>-2.132047198368459</v>
       </c>
       <c r="G17">
-        <v>-7.58360810564217</v>
+        <v>-6.428035113234425</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.163289196879424</v>
       </c>
       <c r="E18">
-        <v>-21.78814384666661</v>
+        <v>-25.33231164997699</v>
       </c>
       <c r="F18">
-        <v>0.3440962165687817</v>
+        <v>-1.973101717854095</v>
       </c>
       <c r="G18">
-        <v>-6.605098422148319</v>
+        <v>-6.920019488451359</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.82253921854195</v>
       </c>
       <c r="E19">
-        <v>-20.48179275655504</v>
+        <v>-26.12009277407047</v>
       </c>
       <c r="F19">
-        <v>0.4814710099142461</v>
+        <v>-1.671194105862384</v>
       </c>
       <c r="G19">
-        <v>-5.929197533465818</v>
+        <v>-6.323177167476951</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.461280499499211</v>
       </c>
       <c r="E20">
-        <v>-23.5791622387517</v>
+        <v>-25.95309214669912</v>
       </c>
       <c r="F20">
-        <v>1.055098869004848</v>
+        <v>-1.324356674310231</v>
       </c>
       <c r="G20">
-        <v>-6.140751389172911</v>
+        <v>-6.873668328980734</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.077220025678726</v>
       </c>
       <c r="E21">
-        <v>-22.88157640499952</v>
+        <v>-27.21379944435082</v>
       </c>
       <c r="F21">
-        <v>0.8789631081475888</v>
+        <v>-0.9433590278014323</v>
       </c>
       <c r="G21">
-        <v>-5.769268541303401</v>
+        <v>-5.832271029776146</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.666136939814053</v>
       </c>
       <c r="E22">
-        <v>-22.13606666577015</v>
+        <v>-27.38202942227433</v>
       </c>
       <c r="F22">
-        <v>1.198215905186518</v>
+        <v>-0.9737824774040498</v>
       </c>
       <c r="G22">
-        <v>-6.296236894041253</v>
+        <v>-6.128846393837434</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.232977249661634</v>
       </c>
       <c r="E23">
-        <v>-23.91563465423268</v>
+        <v>-27.92967186756622</v>
       </c>
       <c r="F23">
-        <v>1.052267509222079</v>
+        <v>-1.023015665622035</v>
       </c>
       <c r="G23">
-        <v>-4.52771067578734</v>
+        <v>-5.45901287558468</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.77650725981561</v>
       </c>
       <c r="E24">
-        <v>-23.81003510308759</v>
+        <v>-28.30093573431529</v>
       </c>
       <c r="F24">
-        <v>1.565634953228628</v>
+        <v>-0.8273577701830007</v>
       </c>
       <c r="G24">
-        <v>-5.226489519321767</v>
+        <v>-6.165952906710927</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.297626599718699</v>
       </c>
       <c r="E25">
-        <v>-24.77572734070275</v>
+        <v>-28.75628344094118</v>
       </c>
       <c r="F25">
-        <v>1.551269405729279</v>
+        <v>-1.111351937089172</v>
       </c>
       <c r="G25">
-        <v>-5.475387465660143</v>
+        <v>-6.026202359493224</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.807307964546031</v>
       </c>
       <c r="E26">
-        <v>-24.63742955679728</v>
+        <v>-28.48710343195073</v>
       </c>
       <c r="F26">
-        <v>1.875820440676514</v>
+        <v>-1.085786033936571</v>
       </c>
       <c r="G26">
-        <v>-5.302114957892545</v>
+        <v>-5.565860208720583</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.311317347977907</v>
       </c>
       <c r="E27">
-        <v>-24.74794235693965</v>
+        <v>-29.32720048249741</v>
       </c>
       <c r="F27">
-        <v>1.423556689770068</v>
+        <v>-0.949884077833284</v>
       </c>
       <c r="G27">
-        <v>-5.33181478836105</v>
+        <v>-5.886940021514059</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.8192601466453152</v>
       </c>
       <c r="E28">
-        <v>-23.33855840028173</v>
+        <v>-29.07999511462663</v>
       </c>
       <c r="F28">
-        <v>1.343465159062995</v>
+        <v>-1.369916881464204</v>
       </c>
       <c r="G28">
-        <v>-5.740284054852861</v>
+        <v>-5.73219074662041</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.3490951322294931</v>
       </c>
       <c r="E29">
-        <v>-23.06528124831934</v>
+        <v>-28.45232236371095</v>
       </c>
       <c r="F29">
-        <v>1.153460871148067</v>
+        <v>-1.292655053805094</v>
       </c>
       <c r="G29">
-        <v>-5.950772726766779</v>
+        <v>-5.636587890438433</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.08501628503334688</v>
       </c>
       <c r="E30">
-        <v>-24.2578509609759</v>
+        <v>-29.04074519100134</v>
       </c>
       <c r="F30">
-        <v>1.158220670244553</v>
+        <v>-1.464121307612772</v>
       </c>
       <c r="G30">
-        <v>-6.515826621599792</v>
+        <v>-5.370289331400286</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.4663721342033319</v>
       </c>
       <c r="E31">
-        <v>-24.43864855636834</v>
+        <v>-29.06433127811504</v>
       </c>
       <c r="F31">
-        <v>0.6495036808373202</v>
+        <v>-1.126447276270387</v>
       </c>
       <c r="G31">
-        <v>-5.047974636415213</v>
+        <v>-5.129555183398321</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.7761105566991676</v>
       </c>
       <c r="E32">
-        <v>-25.0324041069998</v>
+        <v>-27.86563350214869</v>
       </c>
       <c r="F32">
-        <v>0.9703303759415688</v>
+        <v>-1.033329668154292</v>
       </c>
       <c r="G32">
-        <v>-4.70080043143356</v>
+        <v>-5.299073440443898</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.004533082212437</v>
       </c>
       <c r="E33">
-        <v>-24.04906072125412</v>
+        <v>-27.61312240681044</v>
       </c>
       <c r="F33">
-        <v>1.015976733305433</v>
+        <v>-1.456885518349319</v>
       </c>
       <c r="G33">
-        <v>-5.135455466174237</v>
+        <v>-4.707008782071227</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.146673040033762</v>
       </c>
       <c r="E34">
-        <v>-23.54640170782145</v>
+        <v>-27.83613324210843</v>
       </c>
       <c r="F34">
-        <v>0.7858165071723957</v>
+        <v>-1.66224193934033</v>
       </c>
       <c r="G34">
-        <v>-4.910678189113157</v>
+        <v>-4.706611948893378</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.20102755777794</v>
       </c>
       <c r="E35">
-        <v>-22.55579020225732</v>
+        <v>-26.85134869203304</v>
       </c>
       <c r="F35">
-        <v>1.124907046773568</v>
+        <v>-0.910803360504009</v>
       </c>
       <c r="G35">
-        <v>-5.101701149355733</v>
+        <v>-4.785832382766119</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.173767565104091</v>
       </c>
       <c r="E36">
-        <v>-23.60955959243812</v>
+        <v>-26.69878047401546</v>
       </c>
       <c r="F36">
-        <v>0.939470376717676</v>
+        <v>-1.707329148707304</v>
       </c>
       <c r="G36">
-        <v>-4.609450478190506</v>
+        <v>-4.786445907745031</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.07505598436241</v>
       </c>
       <c r="E37">
-        <v>-20.49281537941113</v>
+        <v>-26.51154955428086</v>
       </c>
       <c r="F37">
-        <v>1.262237108279281</v>
+        <v>-1.246673207643096</v>
       </c>
       <c r="G37">
-        <v>-4.929885437069977</v>
+        <v>-4.442673502965598</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.9168768330120657</v>
       </c>
       <c r="E38">
-        <v>-21.89941668448142</v>
+        <v>-26.69402089383721</v>
       </c>
       <c r="F38">
-        <v>1.062361994392594</v>
+        <v>-1.102579526293525</v>
       </c>
       <c r="G38">
-        <v>-4.515557659715707</v>
+        <v>-4.531237791729934</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.7118676183650919</v>
       </c>
       <c r="E39">
-        <v>-20.1182787821381</v>
+        <v>-25.92489184180353</v>
       </c>
       <c r="F39">
-        <v>1.267727527425036</v>
+        <v>-1.083831086865964</v>
       </c>
       <c r="G39">
-        <v>-6.147346130010062</v>
+        <v>-4.903751883712933</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.4727122452458459</v>
       </c>
       <c r="E40">
-        <v>-21.46011906302033</v>
+        <v>-25.08432340177148</v>
       </c>
       <c r="F40">
-        <v>1.315108486130362</v>
+        <v>-0.7195714320981319</v>
       </c>
       <c r="G40">
-        <v>-4.345775717466428</v>
+        <v>-4.735283145992984</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.2120942423014793</v>
       </c>
       <c r="E41">
-        <v>-20.40982591071841</v>
+        <v>-24.19378767629042</v>
       </c>
       <c r="F41">
-        <v>1.088574852486781</v>
+        <v>-1.019172869240449</v>
       </c>
       <c r="G41">
-        <v>-4.847328471609793</v>
+        <v>-4.772875257360425</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.05943984757954131</v>
       </c>
       <c r="E42">
-        <v>-21.97327739468217</v>
+        <v>-24.69267972705148</v>
       </c>
       <c r="F42">
-        <v>1.148379665499294</v>
+        <v>-0.669429524839275</v>
       </c>
       <c r="G42">
-        <v>-4.562070685350982</v>
+        <v>-4.982969706841083</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.331596253157611</v>
       </c>
       <c r="E43">
-        <v>-18.92853740639374</v>
+        <v>-23.64681805123315</v>
       </c>
       <c r="F43">
-        <v>1.156164662350804</v>
+        <v>-0.9481776409835171</v>
       </c>
       <c r="G43">
-        <v>-5.413567644487171</v>
+        <v>-5.420172828302688</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.5953346047033785</v>
       </c>
       <c r="E44">
-        <v>-19.42498321568447</v>
+        <v>-23.81121046189251</v>
       </c>
       <c r="F44">
-        <v>0.8921026718907946</v>
+        <v>-0.1953962785872579</v>
       </c>
       <c r="G44">
-        <v>-5.151132987443873</v>
+        <v>-4.560196170734563</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.846428875737985</v>
       </c>
       <c r="E45">
-        <v>-18.25348274407876</v>
+        <v>-23.60102889637692</v>
       </c>
       <c r="F45">
-        <v>1.437090556397006</v>
+        <v>-0.3667026574861957</v>
       </c>
       <c r="G45">
-        <v>-4.994362996236702</v>
+        <v>-4.735113447594562</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.080429777674304</v>
       </c>
       <c r="E46">
-        <v>-17.95287330838767</v>
+        <v>-23.44310718896164</v>
       </c>
       <c r="F46">
-        <v>0.9740812235414449</v>
+        <v>-0.1147041815131553</v>
       </c>
       <c r="G46">
-        <v>-5.125304891203989</v>
+        <v>-5.172541093091001</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.294537452256558</v>
       </c>
       <c r="E47">
-        <v>-18.2543092331324</v>
+        <v>-21.95283528854136</v>
       </c>
       <c r="F47">
-        <v>1.302853618773346</v>
+        <v>-0.5135175257539633</v>
       </c>
       <c r="G47">
-        <v>-5.533672338656746</v>
+        <v>-5.392989755620016</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.490612026012749</v>
       </c>
       <c r="E48">
-        <v>-17.11837686331252</v>
+        <v>-22.55070667159573</v>
       </c>
       <c r="F48">
-        <v>1.348562932059823</v>
+        <v>-0.5181746072925021</v>
       </c>
       <c r="G48">
-        <v>-4.673027330473297</v>
+        <v>-5.469549840754413</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.669113727348202</v>
       </c>
       <c r="E49">
-        <v>-17.04486917607438</v>
+        <v>-21.5751505570841</v>
       </c>
       <c r="F49">
-        <v>1.135806705059604</v>
+        <v>-0.358190354055028</v>
       </c>
       <c r="G49">
-        <v>-5.575830642314044</v>
+        <v>-4.923100111877674</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.831626477554983</v>
       </c>
       <c r="E50">
-        <v>-16.14345619013359</v>
+        <v>-21.28121948520334</v>
       </c>
       <c r="F50">
-        <v>0.8588321235247552</v>
+        <v>0.004673501639087058</v>
       </c>
       <c r="G50">
-        <v>-4.949330262784589</v>
+        <v>-5.070212958842316</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.982937225274021</v>
       </c>
       <c r="E51">
-        <v>-15.01929402120827</v>
+        <v>-20.58098390262592</v>
       </c>
       <c r="F51">
-        <v>1.022138130047455</v>
+        <v>-0.186521150233664</v>
       </c>
       <c r="G51">
-        <v>-3.989594443645434</v>
+        <v>-4.999929103704956</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.124876350605681</v>
       </c>
       <c r="E52">
-        <v>-16.34739547902797</v>
+        <v>-19.02483376417121</v>
       </c>
       <c r="F52">
-        <v>2.077353946103606</v>
+        <v>-0.1579656691243595</v>
       </c>
       <c r="G52">
-        <v>-5.991450738240915</v>
+        <v>-5.531223460230282</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.259190726010594</v>
       </c>
       <c r="E53">
-        <v>-16.00901258633757</v>
+        <v>-19.33513264188313</v>
       </c>
       <c r="F53">
-        <v>1.341467136887442</v>
+        <v>-0.1496298079499881</v>
       </c>
       <c r="G53">
-        <v>-5.072580904186456</v>
+        <v>-5.560868465062374</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.388129071423252</v>
       </c>
       <c r="E54">
-        <v>-15.26353607279879</v>
+        <v>-20.27800298326835</v>
       </c>
       <c r="F54">
-        <v>1.7723407847188</v>
+        <v>-0.1447399551712626</v>
       </c>
       <c r="G54">
-        <v>-4.7680349368885</v>
+        <v>-5.25006715372411</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.510032225849113</v>
       </c>
       <c r="E55">
-        <v>-13.38135469213372</v>
+        <v>-19.24210070820697</v>
       </c>
       <c r="F55">
-        <v>0.9542004058742568</v>
+        <v>-0.3126922744562651</v>
       </c>
       <c r="G55">
-        <v>-5.273835372481606</v>
+        <v>-5.192797860373449</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.623205624712633</v>
       </c>
       <c r="E56">
-        <v>-15.26875250622278</v>
+        <v>-19.32517324112619</v>
       </c>
       <c r="F56">
-        <v>0.7799450390213528</v>
+        <v>-0.05382663271401682</v>
       </c>
       <c r="G56">
-        <v>-5.167293496462864</v>
+        <v>-5.59525980356111</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.725187791108602</v>
       </c>
       <c r="E57">
-        <v>-13.62610758871719</v>
+        <v>-18.87532230968871</v>
       </c>
       <c r="F57">
-        <v>1.172075943423777</v>
+        <v>-0.3968552309480977</v>
       </c>
       <c r="G57">
-        <v>-5.798117269035203</v>
+        <v>-5.327316475430561</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.810990829651666</v>
       </c>
       <c r="E58">
-        <v>-13.08706229086769</v>
+        <v>-18.77363508361161</v>
       </c>
       <c r="F58">
-        <v>0.9166024661959928</v>
+        <v>0.05142075928127156</v>
       </c>
       <c r="G58">
-        <v>-6.161376271442705</v>
+        <v>-5.681879087605066</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.877083815792598</v>
       </c>
       <c r="E59">
-        <v>-14.02045500400966</v>
+        <v>-18.48559326538945</v>
       </c>
       <c r="F59">
-        <v>0.9633654628188305</v>
+        <v>0.02696155497881056</v>
       </c>
       <c r="G59">
-        <v>-5.697360803030367</v>
+        <v>-5.17870506107062</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.919692153454579</v>
       </c>
       <c r="E60">
-        <v>-15.27773590231838</v>
+        <v>-18.03556789907633</v>
       </c>
       <c r="F60">
-        <v>1.121033600798077</v>
+        <v>-0.4812584139867421</v>
       </c>
       <c r="G60">
-        <v>-5.024041940748478</v>
+        <v>-5.797456750653651</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.934560988927875</v>
       </c>
       <c r="E61">
-        <v>-14.61808965401851</v>
+        <v>-17.53091119099641</v>
       </c>
       <c r="F61">
-        <v>1.280411489096702</v>
+        <v>0.1033560819671894</v>
       </c>
       <c r="G61">
-        <v>-5.296611508294478</v>
+        <v>-5.654142537069078</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.91884031640944</v>
       </c>
       <c r="E62">
-        <v>-13.52055372289667</v>
+        <v>-17.06085903967497</v>
       </c>
       <c r="F62">
-        <v>1.455047904954894</v>
+        <v>-0.2448829472305004</v>
       </c>
       <c r="G62">
-        <v>-5.342349142786192</v>
+        <v>-6.206818891795623</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.869386377357401</v>
       </c>
       <c r="E63">
-        <v>-14.0273701008655</v>
+        <v>-17.09719963876722</v>
       </c>
       <c r="F63">
-        <v>1.387012433428165</v>
+        <v>-0.2874577182647838</v>
       </c>
       <c r="G63">
-        <v>-5.498975543040851</v>
+        <v>-6.032295837368882</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.785022113696261</v>
       </c>
       <c r="E64">
-        <v>-12.33769421831756</v>
+        <v>-17.54193796706383</v>
       </c>
       <c r="F64">
-        <v>1.262034986632998</v>
+        <v>-0.1960109272001352</v>
       </c>
       <c r="G64">
-        <v>-6.096167703790469</v>
+        <v>-6.396139646564794</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.66739978461062</v>
       </c>
       <c r="E65">
-        <v>-13.63200514879845</v>
+        <v>-17.20787856736257</v>
       </c>
       <c r="F65">
-        <v>0.9276611710233662</v>
+        <v>-0.2591010453321511</v>
       </c>
       <c r="G65">
-        <v>-6.756821844060868</v>
+        <v>-6.468188365045747</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.518218289790755</v>
       </c>
       <c r="E66">
-        <v>-12.31660005799875</v>
+        <v>-17.45490742375205</v>
       </c>
       <c r="F66">
-        <v>0.6652062133247877</v>
+        <v>-0.3569386909093979</v>
       </c>
       <c r="G66">
-        <v>-6.419552804057898</v>
+        <v>-6.269223519757004</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.342376366532392</v>
       </c>
       <c r="E67">
-        <v>-12.52649920514426</v>
+        <v>-17.43273758170012</v>
       </c>
       <c r="F67">
-        <v>0.7051724554076554</v>
+        <v>-0.3627480315052309</v>
       </c>
       <c r="G67">
-        <v>-6.07837286865744</v>
+        <v>-6.437185773026277</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.146082637617132</v>
       </c>
       <c r="E68">
-        <v>-14.32577833455443</v>
+        <v>-17.18263534893027</v>
       </c>
       <c r="F68">
-        <v>0.6428088154878946</v>
+        <v>-0.6787552850599918</v>
       </c>
       <c r="G68">
-        <v>-6.503203671501759</v>
+        <v>-6.518458252147633</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.933489255133869</v>
       </c>
       <c r="E69">
-        <v>-10.45508505688603</v>
+        <v>-17.05707961736938</v>
       </c>
       <c r="F69">
-        <v>1.382058796359424</v>
+        <v>-0.3023476223301049</v>
       </c>
       <c r="G69">
-        <v>-7.144392100100817</v>
+        <v>-6.710956283084189</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.711131825454543</v>
       </c>
       <c r="E70">
-        <v>-13.56809137972066</v>
+        <v>-16.64744423119021</v>
       </c>
       <c r="F70">
-        <v>0.6245905311981251</v>
+        <v>-0.4209615507369661</v>
       </c>
       <c r="G70">
-        <v>-6.678695312171802</v>
+        <v>-6.003890936217569</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.484137663052927</v>
       </c>
       <c r="E71">
-        <v>-13.21990275509233</v>
+        <v>-16.73467412864558</v>
       </c>
       <c r="F71">
-        <v>0.08240915545259826</v>
+        <v>-0.3668782713755892</v>
       </c>
       <c r="G71">
-        <v>-6.263315404747314</v>
+        <v>-6.61009538729571</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.254227501198074</v>
       </c>
       <c r="E72">
-        <v>-14.24262273740871</v>
+        <v>-15.95105452229958</v>
       </c>
       <c r="F72">
-        <v>0.4016437284086661</v>
+        <v>-0.7413268451978553</v>
       </c>
       <c r="G72">
-        <v>-6.926052919201422</v>
+        <v>-6.76254981769377</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.025550803168446</v>
       </c>
       <c r="E73">
-        <v>-12.72620637169864</v>
+        <v>-17.43200246329562</v>
       </c>
       <c r="F73">
-        <v>0.8487492354978797</v>
+        <v>-0.5505952507032692</v>
       </c>
       <c r="G73">
-        <v>-6.121674678445645</v>
+        <v>-6.216765828687764</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.8000854923757876</v>
       </c>
       <c r="E74">
-        <v>-13.0179777736905</v>
+        <v>-16.1226319885509</v>
       </c>
       <c r="F74">
-        <v>0.06072166847990441</v>
+        <v>-0.9764224843167718</v>
       </c>
       <c r="G74">
-        <v>-5.634018917760777</v>
+        <v>-6.52079486855668</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.5765674415504982</v>
       </c>
       <c r="E75">
-        <v>-13.91760072555028</v>
+        <v>-16.61026053019902</v>
       </c>
       <c r="F75">
-        <v>0.4214889262775339</v>
+        <v>-0.7167632666026416</v>
       </c>
       <c r="G75">
-        <v>-4.76374287278071</v>
+        <v>-6.582601636006696</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.3570516566269492</v>
       </c>
       <c r="E76">
-        <v>-15.08117686994822</v>
+        <v>-17.57150467848529</v>
       </c>
       <c r="F76">
-        <v>0.5459801214072576</v>
+        <v>-0.7087405283065283</v>
       </c>
       <c r="G76">
-        <v>-5.968624998280811</v>
+        <v>-6.212123924804765</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.140963397912645</v>
       </c>
       <c r="E77">
-        <v>-14.01150068039333</v>
+        <v>-17.00276391966327</v>
       </c>
       <c r="F77">
-        <v>-0.1124096038074007</v>
+        <v>-1.146911264589146</v>
       </c>
       <c r="G77">
-        <v>-6.137219051741134</v>
+        <v>-5.962729936994077</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.07423838687397655</v>
       </c>
       <c r="E78">
-        <v>-14.07406880900187</v>
+        <v>-17.82778273649516</v>
       </c>
       <c r="F78">
-        <v>0.05663450371449165</v>
+        <v>-0.7586032757506418</v>
       </c>
       <c r="G78">
-        <v>-5.785204526287556</v>
+        <v>-5.088451620555833</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.2865157930855811</v>
       </c>
       <c r="E79">
-        <v>-14.7377561319208</v>
+        <v>-18.1906778824247</v>
       </c>
       <c r="F79">
-        <v>-0.02997545008521066</v>
+        <v>-0.8156380281681934</v>
       </c>
       <c r="G79">
-        <v>-4.87330538029137</v>
+        <v>-5.907123687947956</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.4954629077438998</v>
       </c>
       <c r="E80">
-        <v>-15.91183990097055</v>
+        <v>-18.38589127432562</v>
       </c>
       <c r="F80">
-        <v>0.2236996415110959</v>
+        <v>-1.189404027250553</v>
       </c>
       <c r="G80">
-        <v>-4.457630458728086</v>
+        <v>-5.350896720577497</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.7007554357039774</v>
       </c>
       <c r="E81">
-        <v>-16.32342314326106</v>
+        <v>-19.24428529736383</v>
       </c>
       <c r="F81">
-        <v>0.3456991074931987</v>
+        <v>-1.414806939389312</v>
       </c>
       <c r="G81">
-        <v>-5.13644754911886</v>
+        <v>-4.910511101459326</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.8976730022677556</v>
       </c>
       <c r="E82">
-        <v>-16.8166917458883</v>
+        <v>-19.6845506170636</v>
       </c>
       <c r="F82">
-        <v>-0.4568174337671427</v>
+        <v>-1.286323841745498</v>
       </c>
       <c r="G82">
-        <v>-4.453978027045118</v>
+        <v>-4.712961279738965</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.083186929099131</v>
       </c>
       <c r="E83">
-        <v>-15.85105350002036</v>
+        <v>-19.81678886564615</v>
       </c>
       <c r="F83">
-        <v>0.2050149863735503</v>
+        <v>-1.206389700844956</v>
       </c>
       <c r="G83">
-        <v>-4.747872156411332</v>
+        <v>-4.654295238032058</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.253908009080004</v>
       </c>
       <c r="E84">
-        <v>-17.44560423038443</v>
+        <v>-20.08580897600059</v>
       </c>
       <c r="F84">
-        <v>-0.2493403922249645</v>
+        <v>-1.733714307221274</v>
       </c>
       <c r="G84">
-        <v>-4.62808075159269</v>
+        <v>-4.720989319356638</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.403364712333935</v>
       </c>
       <c r="E85">
-        <v>-18.68945779647999</v>
+        <v>-21.52281594117994</v>
       </c>
       <c r="F85">
-        <v>-0.76762171166492</v>
+        <v>-1.521345756165565</v>
       </c>
       <c r="G85">
-        <v>-3.764472548298326</v>
+        <v>-4.563227245204845</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.526799820920046</v>
       </c>
       <c r="E86">
-        <v>-19.10863310907228</v>
+        <v>-22.5405479166952</v>
       </c>
       <c r="F86">
-        <v>-0.3213752215724096</v>
+        <v>-1.544700746720094</v>
       </c>
       <c r="G86">
-        <v>-4.175957224792874</v>
+        <v>-4.060690240350631</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.619184399123722</v>
       </c>
       <c r="E87">
-        <v>-21.26472708303244</v>
+        <v>-22.59543260435281</v>
       </c>
       <c r="F87">
-        <v>-0.7690730113546248</v>
+        <v>-1.834592889534198</v>
       </c>
       <c r="G87">
-        <v>-4.040749373163708</v>
+        <v>-4.593859111492377</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.674782807884043</v>
       </c>
       <c r="E88">
-        <v>-21.78796525857964</v>
+        <v>-23.6625836414222</v>
       </c>
       <c r="F88">
-        <v>-0.4424088111628481</v>
+        <v>-1.90131539872749</v>
       </c>
       <c r="G88">
-        <v>-4.139683539443945</v>
+        <v>-4.422035566972847</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.688707461919378</v>
       </c>
       <c r="E89">
-        <v>-22.92034247950547</v>
+        <v>-24.75127323242216</v>
       </c>
       <c r="F89">
-        <v>-0.7859559673910815</v>
+        <v>-2.233175119269625</v>
       </c>
       <c r="G89">
-        <v>-3.874405781540925</v>
+        <v>-4.136686404653347</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.656336412193556</v>
       </c>
       <c r="E90">
-        <v>-25.99052088715847</v>
+        <v>-27.34460898823762</v>
       </c>
       <c r="F90">
-        <v>-0.6886981789957943</v>
+        <v>-1.871521508351</v>
       </c>
       <c r="G90">
-        <v>-3.407189540259882</v>
+        <v>-3.758462614249584</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.575398513723188</v>
       </c>
       <c r="E91">
-        <v>-27.18880126538668</v>
+        <v>-27.32166664887927</v>
       </c>
       <c r="F91">
-        <v>-1.584730773092978</v>
+        <v>-2.560006649676767</v>
       </c>
       <c r="G91">
-        <v>-4.269693398592205</v>
+        <v>-3.402396213190598</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.445259671290102</v>
       </c>
       <c r="E92">
-        <v>-27.26397023715475</v>
+        <v>-29.03121772422218</v>
       </c>
       <c r="F92">
-        <v>-0.6794212924518427</v>
+        <v>-2.704990825984348</v>
       </c>
       <c r="G92">
-        <v>-3.626502528891763</v>
+        <v>-3.627471115135066</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.267617607088867</v>
       </c>
       <c r="E93">
-        <v>-29.72392561127334</v>
+        <v>-30.61133396862681</v>
       </c>
       <c r="F93">
-        <v>-1.176869171711391</v>
+        <v>-2.896324643580769</v>
       </c>
       <c r="G93">
-        <v>-3.499027702741474</v>
+        <v>-3.863853151903645</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.049237370566687</v>
       </c>
       <c r="E94">
-        <v>-31.57461526706791</v>
+        <v>-32.01498234044514</v>
       </c>
       <c r="F94">
-        <v>-1.254295844483658</v>
+        <v>-3.376263321047344</v>
       </c>
       <c r="G94">
-        <v>-3.716038014643993</v>
+        <v>-4.075125047194897</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.7991665186978855</v>
       </c>
       <c r="E95">
-        <v>-33.39864545936839</v>
+        <v>-34.33590481225377</v>
       </c>
       <c r="F95">
-        <v>-2.214249409217865</v>
+        <v>-3.788579882321187</v>
       </c>
       <c r="G95">
-        <v>-3.725303547197854</v>
+        <v>-4.223378789545856</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.5302719817041014</v>
       </c>
       <c r="E96">
-        <v>-36.67021723737366</v>
+        <v>-36.25450777963193</v>
       </c>
       <c r="F96">
-        <v>-2.696548933782418</v>
+        <v>-3.86067932432605</v>
       </c>
       <c r="G96">
-        <v>-3.840309457180985</v>
+        <v>-4.380409855212137</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.2594777965960859</v>
       </c>
       <c r="E97">
-        <v>-38.06903127120988</v>
+        <v>-38.18185741006018</v>
       </c>
       <c r="F97">
-        <v>-2.204733952861907</v>
+        <v>-4.141684741642921</v>
       </c>
       <c r="G97">
-        <v>-4.024510541806983</v>
+        <v>-4.408942682848414</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.007158190895243508</v>
       </c>
       <c r="E98">
-        <v>-38.83763701861663</v>
+        <v>-39.50769121449651</v>
       </c>
       <c r="F98">
-        <v>-2.663338856236783</v>
+        <v>-4.486716332256971</v>
       </c>
       <c r="G98">
-        <v>-4.295646810572462</v>
+        <v>-5.024511874774878</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.2104107534259559</v>
       </c>
       <c r="E99">
-        <v>-41.96896730981641</v>
+        <v>-41.94701343475336</v>
       </c>
       <c r="F99">
-        <v>-2.592262447974377</v>
+        <v>-4.543862085906498</v>
       </c>
       <c r="G99">
-        <v>-4.043736064975941</v>
+        <v>-4.716702476738031</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.3679953393649</v>
       </c>
       <c r="E100">
-        <v>-42.21290825358587</v>
+        <v>-44.76550723612176</v>
       </c>
       <c r="F100">
-        <v>-3.111718392391502</v>
+        <v>-4.730962946074613</v>
       </c>
       <c r="G100">
-        <v>-5.528978219881926</v>
+        <v>-4.955149612478181</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.454620255262922</v>
       </c>
       <c r="E101">
-        <v>-48.33963942083795</v>
+        <v>-46.46916801950323</v>
       </c>
       <c r="F101">
-        <v>-3.615606828207816</v>
+        <v>-5.062836748862596</v>
       </c>
       <c r="G101">
-        <v>-4.427492023168274</v>
+        <v>-5.246124929391529</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.4460657831019755</v>
       </c>
       <c r="E102">
-        <v>-49.43759794121209</v>
+        <v>-48.967045327926</v>
       </c>
       <c r="F102">
-        <v>-4.191622042153286</v>
+        <v>-5.000929539381778</v>
       </c>
       <c r="G102">
-        <v>-5.13445294025125</v>
+        <v>-6.175925951048979</v>
       </c>
     </row>
   </sheetData>
